--- a/data/trans_dic/IP31KM05_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM05_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>69,5%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>63,15; 83,6</t>
+          <t>54,41; 74,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,67; 72,32</t>
+          <t>64,35; 82,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60,12; 75,49</t>
+          <t>62,06; 76,3</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,83; 89,54</t>
+          <t>62,81; 78,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,96; 78,89</t>
+          <t>61,52; 77,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,94; 82,36</t>
+          <t>64,57; 76,24</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,2%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61,15; 79,06</t>
+          <t>70,93; 87,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71,25; 87,05</t>
+          <t>59,49; 78,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68,52; 81,77</t>
+          <t>69,07; 81,61</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,99%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,92; 80,22</t>
+          <t>72,94; 93,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,29; 93,73</t>
+          <t>58,93; 79,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70,99; 85,86</t>
+          <t>70,73; 84,76</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>91,06; 100,0</t>
+          <t>91,87; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>92,22; 100,0</t>
+          <t>90,55; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94,32; 99,59</t>
+          <t>94,62; 99,66</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>80,92%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69,06; 87,24</t>
+          <t>73,28; 89,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73,25; 89,78</t>
+          <t>67,69; 87,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74,73; 86,93</t>
+          <t>73,82; 86,99</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,14%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>71,85; 86,72</t>
+          <t>72,13; 84,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>72,63; 85,82</t>
+          <t>75,09; 87,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74,54; 84,5</t>
+          <t>74,91; 83,9</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>88,25; 96,87</t>
+          <t>91,57; 98,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>92,45; 98,09</t>
+          <t>86,36; 96,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>92,01; 96,83</t>
+          <t>91,46; 96,71</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,33%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>77,47; 83,75</t>
+          <t>79,69; 84,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>78,52; 84,14</t>
+          <t>77,33; 82,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>79,07; 83,23</t>
+          <t>79,42; 83,23</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>68</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53332</t>
+          <t>39297</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46562</t>
+          <t>40752</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99894</t>
+          <t>80049</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>45093; 59691</t>
+          <t>32791; 44899</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38549; 53953</t>
+          <t>35340; 45476</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87778; 110218</t>
+          <t>71481; 87892</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>98</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>96069</t>
+          <t>81661</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>90343</t>
+          <t>69525</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>186411</t>
+          <t>151186</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83976; 112501</t>
+          <t>72205; 89900</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79592; 99740</t>
+          <t>61109; 77067</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>171260; 207617</t>
+          <t>138372; 163372</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>64</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39217</t>
+          <t>45985</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51779</t>
+          <t>37798</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90996</t>
+          <t>83783</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33971; 43921</t>
+          <t>40643; 50039</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>46050; 56265</t>
+          <t>32194; 42699</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82346; 98280</t>
+          <t>76951; 90923</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>66</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>48927</t>
+          <t>59580</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>64757</t>
+          <t>49818</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113684</t>
+          <t>109398</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41756; 55899</t>
+          <t>50926; 65619</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55239; 70639</t>
+          <t>41521; 55883</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102973; 124544</t>
+          <t>99216; 118903</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>65</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>38949</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40093</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73426</t>
+          <t>73515</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>31141; 34200</t>
+          <t>36362; 39579</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37553; 40719</t>
+          <t>32029; 35370</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70663; 74609</t>
+          <t>70914; 74696</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>58</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>35237</t>
+          <t>39127</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>44637</t>
+          <t>34915</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>79873</t>
+          <t>74042</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>30588; 38637</t>
+          <t>34596; 42320</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>39398; 48286</t>
+          <t>29978; 38554</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73289; 85252</t>
+          <t>67545; 79593</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>142</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>99822</t>
+          <t>110627</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>122748</t>
+          <t>99662</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>222570</t>
+          <t>210289</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>88875; 107264</t>
+          <t>101393; 119338</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>112607; 133063</t>
+          <t>91474; 106334</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>207760; 235541</t>
+          <t>196568; 220149</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>173</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>120341</t>
+          <t>150785</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>147843</t>
+          <t>128319</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>268183</t>
+          <t>279103</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>113552; 124639</t>
+          <t>143885; 154467</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>142527; 151210</t>
+          <t>119084; 133044</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>260227; 273856</t>
+          <t>269855; 285341</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>734</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>526278</t>
+          <t>566010</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>608760</t>
+          <t>495355</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1135038</t>
+          <t>1061364</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>506008; 547004</t>
+          <t>547310; 583530</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>584740; 626642</t>
+          <t>478057; 510739</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1105313; 1163495</t>
+          <t>1036479; 1086227</t>
         </is>
       </c>
     </row>
